--- a/out.xlsx
+++ b/out.xlsx
@@ -483,8 +483,10 @@
       <c r="F2" t="n">
         <v>1087.249387986958</v>
       </c>
-      <c r="G2" t="n">
-        <v>270.110630164189</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[1699.4226472452283, 31.91912453621626, 31.829772517085075, 31.765862368047237, 32.48662035912275, 31.398748978972435, 31.951635144650936]</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>2.978405034169555</v>

--- a/out.xlsx
+++ b/out.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4833374.937986562</t>
+          <t>2024-10-06 02:56:14.937987</t>
         </is>
       </c>
       <c r="D2" t="n">
